--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Districts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mail-In" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Senate" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -514,7 +515,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -547,7 +548,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>September 22, 2026</t>
+          <t>September 28, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -556,6 +557,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10071,4 +10073,801 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Senate 2026 — 35 seats up (edit the blue Dem win % cells)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Per-race Democratic win probability (%). 34 Democratic-held seats are not up; 51 needed for control. Consensus of Cook/markets/forecasters, late Sept 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Dem win %</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>NM</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>RI</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Solid D</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Lean D (flip)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Likely D</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>85</v>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Likely D</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Toss-Up</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Toss-Up</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Toss-Up</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Toss-Up</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Toss-Up</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Toss-Up</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Toss-Up</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Lean R</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Likely R</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Likely R</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>WV</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>WY</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Solid R</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>September 28, 2026</t>
+          <t>October 2, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Districts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mail-In" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Senate" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Polls" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0;-0.0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +58,9 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -93,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +109,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -557,7 +564,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10870,4 +10876,1173 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Pollster</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Start date</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>End date</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Dem %</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Rep %</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>51</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>44</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Pew Research</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="D5" t="n">
+        <v>44</v>
+      </c>
+      <c r="E5" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cygnal</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D6" t="n">
+        <v>52</v>
+      </c>
+      <c r="E6" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CBS News</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Harvard-Harris</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>46293</v>
+      </c>
+      <c r="D8" t="n">
+        <v>51</v>
+      </c>
+      <c r="E8" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>46293</v>
+      </c>
+      <c r="D9" t="n">
+        <v>53</v>
+      </c>
+      <c r="E9" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>46292</v>
+      </c>
+      <c r="D10" t="n">
+        <v>47</v>
+      </c>
+      <c r="E10" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Quinnipiac</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>46289</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>46292</v>
+      </c>
+      <c r="D11" t="n">
+        <v>51</v>
+      </c>
+      <c r="E11" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>46290</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>46292</v>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>46288</v>
+      </c>
+      <c r="D13" t="n">
+        <v>48</v>
+      </c>
+      <c r="E13" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>46286</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>46287</v>
+      </c>
+      <c r="D14" t="n">
+        <v>53</v>
+      </c>
+      <c r="E14" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D15" t="n">
+        <v>52</v>
+      </c>
+      <c r="E15" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Echelon Insights</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D16" t="n">
+        <v>51</v>
+      </c>
+      <c r="E16" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>46286</v>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>46283</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>46285</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>46285</v>
+      </c>
+      <c r="D19" t="n">
+        <v>43</v>
+      </c>
+      <c r="E19" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Quantus Insights</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>46282</v>
+      </c>
+      <c r="D21" t="n">
+        <v>49</v>
+      </c>
+      <c r="E21" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D22" t="n">
+        <v>49</v>
+      </c>
+      <c r="E22" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NPR/PBS/Marist</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D23" t="n">
+        <v>53</v>
+      </c>
+      <c r="E23" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Big Data Poll</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D24" t="n">
+        <v>51</v>
+      </c>
+      <c r="E24" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NBC News</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D25" t="n">
+        <v>50</v>
+      </c>
+      <c r="E25" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RMG Research</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D26" t="n">
+        <v>52</v>
+      </c>
+      <c r="E26" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FOX News</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D27" t="n">
+        <v>51</v>
+      </c>
+      <c r="E27" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D28" t="n">
+        <v>51</v>
+      </c>
+      <c r="E28" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D29" t="n">
+        <v>44</v>
+      </c>
+      <c r="E29" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>46278</v>
+      </c>
+      <c r="D30" t="n">
+        <v>49</v>
+      </c>
+      <c r="E30" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NY Times/Siena</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>46278</v>
+      </c>
+      <c r="D31" t="n">
+        <v>51</v>
+      </c>
+      <c r="E31" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CBS News</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>46276</v>
+      </c>
+      <c r="D32" t="n">
+        <v>54</v>
+      </c>
+      <c r="E32" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D33" t="n">
+        <v>47</v>
+      </c>
+      <c r="E33" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Marquette</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D34" t="n">
+        <v>54</v>
+      </c>
+      <c r="E34" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D35" t="n">
+        <v>49</v>
+      </c>
+      <c r="E35" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Quinnipiac</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>46268</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>46271</v>
+      </c>
+      <c r="D36" t="n">
+        <v>49</v>
+      </c>
+      <c r="E36" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>46271</v>
+      </c>
+      <c r="D37" t="n">
+        <v>46</v>
+      </c>
+      <c r="E37" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cygnal</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D38" t="n">
+        <v>51</v>
+      </c>
+      <c r="E38" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Financial Times</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D39" t="n">
+        <v>52</v>
+      </c>
+      <c r="E39" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D40" t="n">
+        <v>46</v>
+      </c>
+      <c r="E40" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>46265</v>
+      </c>
+      <c r="D41" t="n">
+        <v>43</v>
+      </c>
+      <c r="E41" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D42" t="n">
+        <v>47</v>
+      </c>
+      <c r="E42" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Harvard-Harris</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>46262</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D43" t="n">
+        <v>49</v>
+      </c>
+      <c r="E43" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Quantus Insights</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>46260</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>46262</v>
+      </c>
+      <c r="D44" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>46261</v>
+      </c>
+      <c r="D45" t="n">
+        <v>41</v>
+      </c>
+      <c r="E45" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D46" t="n">
+        <v>46</v>
+      </c>
+      <c r="E46" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>46255</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>46258</v>
+      </c>
+      <c r="D47" t="n">
+        <v>41</v>
+      </c>
+      <c r="E47" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D48" t="n">
+        <v>51</v>
+      </c>
+      <c r="E48" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D49" t="n">
+        <v>46</v>
+      </c>
+      <c r="E49" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>46248</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D50" t="n">
+        <v>41</v>
+      </c>
+      <c r="E50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Echelon Insights</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>46247</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>46251</v>
+      </c>
+      <c r="D51" t="n">
+        <v>50</v>
+      </c>
+      <c r="E51" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>46250</v>
+      </c>
+      <c r="D52" t="n">
+        <v>46</v>
+      </c>
+      <c r="E52" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Financial Times</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>46245</v>
+      </c>
+      <c r="D53" t="n">
+        <v>51</v>
+      </c>
+      <c r="E53" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>46244</v>
+      </c>
+      <c r="D54" t="n">
+        <v>46</v>
+      </c>
+      <c r="E54" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Cygnal</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>46240</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>46241</v>
+      </c>
+      <c r="D55" t="n">
+        <v>49</v>
+      </c>
+      <c r="E55" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Quantus Insights</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D56" t="n">
+        <v>49</v>
+      </c>
+      <c r="E56" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RMG Research</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>46238</v>
+      </c>
+      <c r="D57" t="n">
+        <v>47</v>
+      </c>
+      <c r="E57" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D58" t="n">
+        <v>46</v>
+      </c>
+      <c r="E58" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>46232</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>46237</v>
+      </c>
+      <c r="D59" t="n">
+        <v>42</v>
+      </c>
+      <c r="E59" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>46236</v>
+      </c>
+      <c r="D60" t="n">
+        <v>46</v>
+      </c>
+      <c r="E60" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -522,7 +523,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -538,7 +539,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Nate Silver · Silver Bulletin</t>
+          <t>Nate Silver · Silver Bulletin (Oct. 8, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -555,7 +556,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 2, 2026</t>
+          <t>October 9, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -10107,7 +10108,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Per-race Democratic win probability (%). 34 Democratic-held seats are not up; 51 needed for control. Consensus of Cook/markets/forecasters, late Sept 2026.</t>
+          <t>Per-race Democratic win probability (%). 34 Democratic-held seats are not up; 51 needed for control. Decision Desk HQ / The Hill forecast, Oct. 9, 2026.</t>
         </is>
       </c>
     </row>
@@ -10149,7 +10150,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -10166,11 +10167,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -10187,11 +10188,11 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -10208,11 +10209,11 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -10229,11 +10230,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -10250,11 +10251,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -10271,11 +10272,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -10292,11 +10293,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -10313,11 +10314,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Solid D</t>
+          <t>Safe D</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -10334,11 +10335,11 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Lean D (flip)</t>
+          <t>Likely D (flip)</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -10355,7 +10356,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -10376,7 +10377,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -10397,11 +10398,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Toss-Up</t>
+          <t>Lean D</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -10418,11 +10419,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Toss-Up</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -10439,11 +10440,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Toss-Up</t>
+          <t>Toss-Up (flip)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -10460,11 +10461,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Toss-Up</t>
+          <t>Lean D (flip)</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -10481,11 +10482,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Toss-Up</t>
+          <t>Toss-Up (flip)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -10502,7 +10503,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -10523,11 +10524,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Toss-Up</t>
+          <t>Toss-Up (flip)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -10544,7 +10545,7 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
@@ -10565,11 +10566,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -10586,7 +10587,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
@@ -10607,11 +10608,11 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -10628,11 +10629,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -10649,11 +10650,11 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -10670,11 +10671,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -10691,11 +10692,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -10712,11 +10713,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -10733,11 +10734,11 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -10754,11 +10755,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Likely R</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -10779,7 +10780,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -10796,11 +10797,11 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -10817,11 +10818,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -10838,11 +10839,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -10859,11 +10860,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Solid R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -10884,7 +10885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10924,153 +10925,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Economist/YouGov</t>
+          <t>Reuters/Ipsos</t>
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>46300</v>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reuters/Ipsos</t>
+          <t>Economist/YouGov</t>
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C3" s="11" t="n">
         <v>46300</v>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Morning Consult</t>
+          <t>Pew Research</t>
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>46297</v>
+        <v>46293</v>
       </c>
       <c r="C4" s="11" t="n">
         <v>46299</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pew Research</t>
+          <t>Morning Consult</t>
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>46293</v>
+        <v>46297</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>46299</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E5" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cygnal</t>
+          <t>CBS News</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>46296</v>
+        <v>46295</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>46297</v>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CBS News</t>
+          <t>Cygnal</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C7" s="11" t="n">
         <v>46297</v>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Harvard-Harris</t>
+          <t>Economist/YouGov</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>46291</v>
+        <v>46290</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>46293</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E8" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Economist/YouGov</t>
+          <t>Harvard-Harris</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>46293</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E9" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -11171,20 +11172,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Economist/YouGov</t>
+          <t>Wall Street Journal</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="C15" s="11" t="n">
         <v>46286</v>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
@@ -11209,58 +11210,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wall Street Journal</t>
+          <t>Economist/YouGov</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C17" s="11" t="n">
         <v>46286</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Morning Consult</t>
+          <t>Reuters/Ipsos</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="C18" s="11" t="n">
         <v>46285</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E18" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Reuters/Ipsos</t>
+          <t>Morning Consult</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="C19" s="11" t="n">
         <v>46285</v>
       </c>
       <c r="D19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" t="n">
         <v>43</v>
-      </c>
-      <c r="E19" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="20">
@@ -11323,77 +11324,77 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NPR/PBS/Marist</t>
+          <t>RMG Research</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
-        <v>46279</v>
+        <v>46273</v>
       </c>
       <c r="C23" s="11" t="n">
         <v>46280</v>
       </c>
       <c r="D23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Big Data Poll</t>
+          <t>NBC News</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>46278</v>
+        <v>46276</v>
       </c>
       <c r="C24" s="11" t="n">
         <v>46280</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E24" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NBC News</t>
+          <t>Big Data Poll</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C25" s="11" t="n">
         <v>46280</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E25" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RMG Research</t>
+          <t>NPR/PBS/Marist</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>46273</v>
+        <v>46279</v>
       </c>
       <c r="C26" s="11" t="n">
         <v>46280</v>
       </c>
       <c r="D26" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E26" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -11456,17 +11457,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Morning Consult</t>
+          <t>NY Times/Siena</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="C30" s="11" t="n">
         <v>46278</v>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E30" t="n">
         <v>43</v>
@@ -11475,17 +11476,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NY Times/Siena</t>
+          <t>Morning Consult</t>
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="C31" s="11" t="n">
         <v>46278</v>
       </c>
       <c r="D31" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E31" t="n">
         <v>43</v>
@@ -11513,39 +11514,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rasmussen Reports</t>
+          <t>Marquette</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="C33" s="11" t="n">
         <v>46274</v>
       </c>
       <c r="D33" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E33" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marquette</t>
+          <t>Rasmussen Reports</t>
         </is>
       </c>
       <c r="B34" s="11" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="C34" s="11" t="n">
         <v>46274</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E34" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35">
@@ -11570,77 +11571,77 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Quinnipiac</t>
+          <t>Morning Consult</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="C36" s="11" t="n">
         <v>46271</v>
       </c>
       <c r="D36" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E36" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Morning Consult</t>
+          <t>Quinnipiac</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="C37" s="11" t="n">
         <v>46271</v>
       </c>
       <c r="D37" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E37" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cygnal</t>
+          <t>Financial Times</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="C38" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="D38" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E38" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Financial Times</t>
+          <t>Cygnal</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="C39" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="D39" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E39" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
@@ -11798,20 +11799,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Echelon Insights</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="C48" s="11" t="n">
         <v>46251</v>
       </c>
       <c r="D48" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E48" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -11855,20 +11856,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Echelon Insights</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="C51" s="11" t="n">
         <v>46251</v>
       </c>
       <c r="D51" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E51" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
@@ -11950,77 +11951,77 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quantus Insights</t>
+          <t>RMG Research</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="C56" s="11" t="n">
         <v>46238</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E56" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RMG Research</t>
+          <t>Quantus Insights</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="C57" s="11" t="n">
         <v>46238</v>
       </c>
       <c r="D57" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E57" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Economist/YouGov</t>
+          <t>Reuters/Ipsos</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="C58" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="D58" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E58" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Reuters/Ipsos</t>
+          <t>Economist/YouGov</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="C59" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="D59" t="n">
+        <v>46</v>
+      </c>
+      <c r="E59" t="n">
         <v>42</v>
-      </c>
-      <c r="E59" t="n">
-        <v>37</v>
       </c>
     </row>
     <row r="60">
@@ -12040,6 +12041,386 @@
       </c>
       <c r="E60" t="n">
         <v>42</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Marquette</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D61" t="n">
+        <v>51</v>
+      </c>
+      <c r="E61" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Big Data Poll</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>46232</v>
+      </c>
+      <c r="D62" t="n">
+        <v>50</v>
+      </c>
+      <c r="E62" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Quinnipiac</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D63" t="n">
+        <v>48</v>
+      </c>
+      <c r="E63" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D64" t="n">
+        <v>47</v>
+      </c>
+      <c r="E64" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>46230</v>
+      </c>
+      <c r="D65" t="n">
+        <v>46</v>
+      </c>
+      <c r="E65" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>46229</v>
+      </c>
+      <c r="D66" t="n">
+        <v>46</v>
+      </c>
+      <c r="E66" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>46229</v>
+      </c>
+      <c r="D67" t="n">
+        <v>40</v>
+      </c>
+      <c r="E67" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Daily Mail</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D68" t="n">
+        <v>50</v>
+      </c>
+      <c r="E68" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>FOX News</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D69" t="n">
+        <v>53</v>
+      </c>
+      <c r="E69" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D70" t="n">
+        <v>46</v>
+      </c>
+      <c r="E70" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>46222</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>46223</v>
+      </c>
+      <c r="D71" t="n">
+        <v>53</v>
+      </c>
+      <c r="E71" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>46222</v>
+      </c>
+      <c r="D72" t="n">
+        <v>46</v>
+      </c>
+      <c r="E72" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>RMG Research</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>46217</v>
+      </c>
+      <c r="D73" t="n">
+        <v>47</v>
+      </c>
+      <c r="E73" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Wash Post/Ipsos</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>46216</v>
+      </c>
+      <c r="D74" t="n">
+        <v>48</v>
+      </c>
+      <c r="E74" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Echelon Insights</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>46216</v>
+      </c>
+      <c r="D75" t="n">
+        <v>50</v>
+      </c>
+      <c r="E75" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>46216</v>
+      </c>
+      <c r="D76" t="n">
+        <v>46</v>
+      </c>
+      <c r="E76" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>46216</v>
+      </c>
+      <c r="D77" t="n">
+        <v>46</v>
+      </c>
+      <c r="E77" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>46211</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>46215</v>
+      </c>
+      <c r="D78" t="n">
+        <v>49</v>
+      </c>
+      <c r="E78" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Harvard-Harris</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>46215</v>
+      </c>
+      <c r="D79" t="n">
+        <v>51</v>
+      </c>
+      <c r="E79" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2Way/HarrisX</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>46213</v>
+      </c>
+      <c r="D80" t="n">
+        <v>51</v>
+      </c>
+      <c r="E80" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -497,6 +497,11 @@
           <t>Edit the blue cells, save, then load this file on the page (or run update_forecast.py).</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>October 11, 2026</t>
+        </is>
+      </c>
     </row>
     <row r="3"/>
     <row r="4">
@@ -523,7 +528,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -539,7 +544,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Nate Silver · Silver Bulletin (Oct. 8, 2026)</t>
+          <t>RealClearPolitics average (Oct. 10, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -556,7 +561,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 9, 2026</t>
+          <t>October 11, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -20,9 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0;-0.0"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -98,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -111,6 +112,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -499,7 +501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>October 11, 2026</t>
+          <t>October 16, 2026</t>
         </is>
       </c>
     </row>
@@ -528,7 +530,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -544,7 +546,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>RealClearPolitics average (Oct. 10, 2026)</t>
+          <t>RealClearPolitics average (Oct. 16, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -561,7 +563,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 11, 2026</t>
+          <t>October 16, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -10890,7 +10892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12428,6 +12430,215 @@
         <v>49</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FOX News</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C81" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D81" t="n">
+        <v>54</v>
+      </c>
+      <c r="E81" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="n">
+        <v>46305</v>
+      </c>
+      <c r="C82" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D82" t="n">
+        <v>49</v>
+      </c>
+      <c r="E82" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>RMG Research</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C83" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="D83" t="n">
+        <v>54</v>
+      </c>
+      <c r="E83" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>46306</v>
+      </c>
+      <c r="D84" t="n">
+        <v>50</v>
+      </c>
+      <c r="E84" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>AP/NORC</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C85" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D85" t="n">
+        <v>47</v>
+      </c>
+      <c r="E85" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cygnal</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C86" s="12" t="n">
+        <v>46305</v>
+      </c>
+      <c r="D86" t="n">
+        <v>51</v>
+      </c>
+      <c r="E86" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NewsNation</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C87" s="12" t="n">
+        <v>46304</v>
+      </c>
+      <c r="D87" t="n">
+        <v>49</v>
+      </c>
+      <c r="E87" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Center Square/NPI</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C88" s="12" t="n">
+        <v>46302</v>
+      </c>
+      <c r="D88" t="n">
+        <v>47</v>
+      </c>
+      <c r="E88" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Financial Times</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="n">
+        <v>46298</v>
+      </c>
+      <c r="C89" s="12" t="n">
+        <v>46301</v>
+      </c>
+      <c r="D89" t="n">
+        <v>52</v>
+      </c>
+      <c r="E89" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C90" s="12" t="n">
+        <v>46302</v>
+      </c>
+      <c r="D90" t="n">
+        <v>49</v>
+      </c>
+      <c r="E90" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>THP/MM</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C91" s="12" t="n">
+        <v>46301</v>
+      </c>
+      <c r="D91" t="n">
+        <v>54</v>
+      </c>
+      <c r="E91" t="n">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>October 16, 2026</t>
+          <t>October 18, 2026</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>RealClearPolitics average (Oct. 16, 2026)</t>
+          <t>RealClearPolitics average (Oct. 18, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 16, 2026</t>
+          <t>October 18, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>October 18, 2026</t>
+          <t>October 20, 2026</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>RealClearPolitics average (Oct. 18, 2026)</t>
+          <t>RealClearPolitics average (Oct. 20, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 18, 2026</t>
+          <t>October 20, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -10892,7 +10892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12639,6 +12639,63 @@
         <v>42</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C92" s="12" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D92" t="n">
+        <v>47</v>
+      </c>
+      <c r="E92" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C93" s="12" t="n">
+        <v>46313</v>
+      </c>
+      <c r="D93" t="n">
+        <v>50</v>
+      </c>
+      <c r="E93" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D94" t="n">
+        <v>48</v>
+      </c>
+      <c r="E94" t="n">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>October 20, 2026</t>
+          <t>October 21, 2026</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>RealClearPolitics average (Oct. 20, 2026)</t>
+          <t>Avg of RCP, Silver Bulletin, DDHQ, 50+1 (Oct. 21, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 20, 2026</t>
+          <t>October 21, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -10115,10 +10115,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Per-race Democratic win probability (%). 34 Democratic-held seats are not up; 51 needed for control. Decision Desk HQ / The Hill forecast, Oct. 9, 2026.</t>
-        </is>
-      </c>
-    </row>
+          <t>Per-race Democratic win probability (%). Blend of Silver Bulletin, Decision Desk HQ, and Cook/Sabato/Inside Elections consensus, Oct. 21, 2026. 34 Democratic-held seats not up; 51 needed for control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10153,7 +10154,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -10195,7 +10196,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
@@ -10237,7 +10238,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
@@ -10258,7 +10259,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -10321,7 +10322,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
@@ -10342,7 +10343,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
@@ -10363,7 +10364,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -10384,7 +10385,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
@@ -10405,11 +10406,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Lean D</t>
+          <t>Likely D</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -10426,7 +10427,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
@@ -10447,11 +10448,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Toss-Up (flip)</t>
+          <t>Lean D (flip)</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -10468,7 +10469,7 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
@@ -10489,11 +10490,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Toss-Up (flip)</t>
+          <t>Lean D (flip)</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -10510,7 +10511,7 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -10531,7 +10532,7 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -10552,11 +10553,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Lean R</t>
+          <t>Toss-Up</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -10573,7 +10574,7 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
@@ -10594,11 +10595,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Lean R</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -10657,7 +10658,7 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
@@ -10720,7 +10721,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
@@ -10741,11 +10742,11 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>Likely R</t>
+          <t>Safe R</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -10762,7 +10763,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
@@ -10892,7 +10893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12696,6 +12697,25 @@
         <v>44</v>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Echelon Insights</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D95" t="n">
+        <v>50</v>
+      </c>
+      <c r="E95" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>October 21, 2026</t>
+          <t>October 24, 2026</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Avg of RCP, Silver Bulletin, DDHQ, 50+1 (Oct. 21, 2026)</t>
+          <t>Avg of RCP, Silver Bulletin, DDHQ, 50+1 (Oct. 24, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 21, 2026</t>
+          <t>October 24, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -10119,7 +10119,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10893,7 +10892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12716,6 +12715,25 @@
         <v>45</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D96" t="n">
+        <v>50</v>
+      </c>
+      <c r="E96" t="n">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>October 24, 2026</t>
+          <t>October 26, 2026</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -546,7 +546,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Avg of RCP, Silver Bulletin, DDHQ, 50+1 (Oct. 24, 2026)</t>
+          <t>Avg of RCP, Silver Bulletin, DDHQ, 50+1 (Oct. 26, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 24, 2026</t>
+          <t>October 26, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -10892,7 +10892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12734,6 +12734,25 @@
         <v>43</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CBS News</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="n">
+        <v>46316</v>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>46318</v>
+      </c>
+      <c r="D97" t="n">
+        <v>53</v>
+      </c>
+      <c r="E97" t="n">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -12,6 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mail-In" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Senate" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Polls" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundraising" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pollsters" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -505,7 +507,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10892,7 +10893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12753,6 +12754,2449 @@
         <v>45</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NY Times/Siena</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D98" t="n">
+        <v>52</v>
+      </c>
+      <c r="E98" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>46313</v>
+      </c>
+      <c r="D99" t="n">
+        <v>49</v>
+      </c>
+      <c r="E99" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>46314</v>
+      </c>
+      <c r="D100" t="n">
+        <v>52</v>
+      </c>
+      <c r="E100" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Financial Times</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D101" t="n">
+        <v>53</v>
+      </c>
+      <c r="E101" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ABC/Wash Post/Ipsos</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="D102" t="n">
+        <v>52</v>
+      </c>
+      <c r="E102" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NBC News Decision Desk</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D103" t="n">
+        <v>55</v>
+      </c>
+      <c r="E103" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>THP/MM</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n">
+        <v>46272</v>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>46278</v>
+      </c>
+      <c r="D104" t="n">
+        <v>51</v>
+      </c>
+      <c r="E104" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fundraising adjustment (House only). Q3 2026 FEC filings through Oct. 14, 2026. Rule: 0.75 pts per doubling of the receipts ratio, capped at 1.5, halved when the money edge is the incumbent's. Senate rows are informational only (its win odds come from models that already include fundraising).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Race</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dem candidate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dem receipts</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Dem status</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Rep candidate</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rep receipts</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Rep status</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Adjustment (pts, Dem +)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MI-04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>McCann</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4699153</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Huizenga</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5562775</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MI-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hines</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4159693</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bouchard</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2884259</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>WI-03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Cooke</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12675997</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Van Orden</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>9101596</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WI-01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Berman</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1977099</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Steil</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>6393553</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TX-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Stout</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1117715</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Herrera</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3115205</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PA-08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cognetti</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7502359</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Bresnahan</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>6519139</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PA-10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Stelson</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>9234260</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Perry</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6791519</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FL-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Dandiya</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4619822</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Askar</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>7418255</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FL-27</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rodriguez</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1567393</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Salazar</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2519401</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NC-03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>366581</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Murphy</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2897749</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NC-07</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hardy</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>390475</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Rouzer</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>2534038</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NC-01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Davis</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5805482</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Buckhout</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>4787737</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NC-09</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ojeda</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2930069</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Hudson</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4173708</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NC-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Caldwell</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>78144</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Moore</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2091455</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NC-11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ager</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5869453</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Edwards</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1025828</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NC-13</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Barringer</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1215151</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Knott</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1697075</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>OH-10</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Knickerbocker</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1015878</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Turner</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1315094</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OH-15</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Leonard</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1329844</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Carey</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4184981</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>OH-09</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Kaptur</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5910481</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Merrin</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2217821</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>OH-07</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Poindexter</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3720342</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Miller</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3324942</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NJ-02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mullock</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>960948</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Van Drew</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2414607</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MT-01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Forstag</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4312110</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Flint</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2856139</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AZ-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Mendoza</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>11242473</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ciscomani</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>7649794</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AZ-01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Shah</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5654454</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Feely</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>3799654</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ME-02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Dunlap</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2964964</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LePage</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>3299130</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VA-02</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Luria</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8044064</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kiggans</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>7589812</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NY-11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DeCillis</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>183306</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Malliotakis</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>3315037</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NY-02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Halpin</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>586334</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Garbarino</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>4057667</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NY-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gallant</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1735638</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>4486089</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MO-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wellman</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2178965</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Wagner</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>4189876</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WA-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gluesenkamp Perez</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9472267</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Braun</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>3311756</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>IA-02</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3917994</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Mitchell</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2916069</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senate (informational)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Dem candidate</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dem receipts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Rep candidate</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rep receipts</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ossoff</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>136610982</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Collins</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>10679277</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Flanagan</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11563963</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Tafoya</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>12501786</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cooper</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>49585341</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Whatley</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>13668468</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pappas</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>23703648</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sununu</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>5681528</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>El-Sayed</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>53830872</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Rogers</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>23016439</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AK</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Peltola</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>36887509</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sullivan</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>14107205</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Talarico</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>146349912</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Paxton</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>22327474</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>26872874</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Collins</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>25225468</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Brown</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>68409200</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Husted</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>19894786</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Turek</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>24290521</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Hinson</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>14147973</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Hamilton</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>19175044</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Marshall</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>7546611</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Andrews</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>24216841</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Graham</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>21650508</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Vindman</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>20487916</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Moody</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>14524032</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Osborn (I)</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>11029845</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Ricketts</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>14546959</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Neill</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>310977</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Daines</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>8405689</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Pollster weighting and population defaults. Weight = 538 pollster grade (2023). Pop = usual generic-ballot sample (LV / RV / A); add a Pop column to the Polls sheet to override per poll. LV adjustment (Dem margin): RV +0.5, A +1.0 (Silver Bulletin's current likely-voter screen).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Pollster</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>538 grade</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Default population</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2Way/HarrisX</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABC/Wash Post/Ipsos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AP/NORC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ActiVote</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Big Data Poll</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CBS News</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Center Square/NPI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cygnal</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Daily Mail</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Echelon Insights</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FOX News</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Financial Times</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Harvard-Harris</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Marquette</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>A/B</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NBC News</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NBC News Decision Desk</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NPR/PBS/Marist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NY Times/Siena</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NewsNation</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Northgate Insights</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pew Research</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B/C</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Quantus Insights</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Quinnipiac</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RMG Research</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>THP/MM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NR</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Wall Street Journal</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Wash Post/Ipsos</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -507,6 +507,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10893,7 +10894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12885,6 +12886,25 @@
       </c>
       <c r="E104" t="n">
         <v>42</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>46320</v>
+      </c>
+      <c r="D105" t="n">
+        <v>50</v>
+      </c>
+      <c r="E105" t="n">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/house-polling.xlsx
+++ b/house-polling.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>October 26, 2026</t>
+          <t>October 27, 2026</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Avg of RCP, Silver Bulletin, DDHQ, 50+1 (Oct. 26, 2026)</t>
+          <t>Avg of RCP, Silver Bulletin, DDHQ, 50+1 (Oct. 27, 2026)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>October 26, 2026</t>
+          <t>October 27, 2026</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -10894,7 +10894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12905,6 +12905,174 @@
       </c>
       <c r="E105" t="n">
         <v>43</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Harvard-Harris</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>46321</v>
+      </c>
+      <c r="D106" t="n">
+        <v>52</v>
+      </c>
+      <c r="E106" t="n">
+        <v>48</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NPR/PBS/Marist</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>46320</v>
+      </c>
+      <c r="D107" t="n">
+        <v>52</v>
+      </c>
+      <c r="E107" t="n">
+        <v>44</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Economist/YouGov</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="n">
+        <v>46318</v>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>46321</v>
+      </c>
+      <c r="D108" t="n">
+        <v>50</v>
+      </c>
+      <c r="E108" t="n">
+        <v>41</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Reuters/Ipsos</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="n">
+        <v>46317</v>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>46321</v>
+      </c>
+      <c r="D109" t="n">
+        <v>53</v>
+      </c>
+      <c r="E109" t="n">
+        <v>44</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Rasmussen Reports</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="n">
+        <v>46310</v>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>46316</v>
+      </c>
+      <c r="D110" t="n">
+        <v>48</v>
+      </c>
+      <c r="E110" t="n">
+        <v>43</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Echelon Insights</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>46318</v>
+      </c>
+      <c r="D111" t="n">
+        <v>51</v>
+      </c>
+      <c r="E111" t="n">
+        <v>46</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Morning Consult</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C112" s="12" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D112" t="n">
+        <v>48</v>
+      </c>
+      <c r="E112" t="n">
+        <v>42</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>RV</t>
+        </is>
       </c>
     </row>
   </sheetData>
